--- a/data/circular.xlsx
+++ b/data/circular.xlsx
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-10-13 07:28:38</v>
+        <v>2025-10-13 19:28:38</v>
       </c>
       <c r="B2" t="str">
-        <v>-10.18</v>
+        <v>1.82</v>
       </c>
       <c r="C2" t="str">
         <v>OHP/T193</v>

--- a/data/circular.xlsx
+++ b/data/circular.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I260"/>
+  <dimension ref="A1:I282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,23 +1559,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.73</v>
+        <v>16.09</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H33" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -1590,27 +1594,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16.09</v>
+        <v>15.73</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -1656,27 +1656,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16.16</v>
+        <v>15.76</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -1691,23 +1687,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.76</v>
+        <v>16.16</v>
       </c>
       <c r="E37" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H37" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -1959,27 +1959,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16.2</v>
+        <v>15.84</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -1994,23 +1990,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.84</v>
+        <v>16.2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H46" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Bassano Bresciano Observatory</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16.27</v>
+        <v>15.72</v>
       </c>
       <c r="E51" t="n">
         <v>0.01</v>
@@ -2173,11 +2173,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>42275</v>
+        <v>42262</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -2192,11 +2192,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.72</v>
+        <v>16.27</v>
       </c>
       <c r="E52" t="n">
         <v>0.01</v>
@@ -2208,11 +2208,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -2460,27 +2460,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>Bassano Bresciano Observatory</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16.58</v>
+        <v>15.84</v>
       </c>
       <c r="E60" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>42269</v>
+        <v>42262</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -2495,23 +2495,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Osservatorio Astronomico "Nastro Verde"</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16.04</v>
+        <v>16.58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H61" t="n">
-        <v>42333</v>
+        <v>42269</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -2526,27 +2530,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>15.84</v>
+        <v>16.04</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -2627,27 +2627,23 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16.53</v>
+        <v>16.12</v>
       </c>
       <c r="E65" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -2662,23 +2658,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16.12</v>
+        <v>16.53</v>
       </c>
       <c r="E66" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H66" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -2860,27 +2860,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Osservatorio Astronomico "Nastro Verde"</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>16.61</v>
+        <v>16.7</v>
       </c>
       <c r="E72" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>42275</v>
+        <v>42269</v>
       </c>
       <c r="I72" t="b">
         <v>0</v>
@@ -2895,27 +2895,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16.7</v>
+        <v>16.61</v>
       </c>
       <c r="E73" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>42269</v>
+        <v>42275</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -2930,23 +2930,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Bassano Bresciano Observatory</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>16.29</v>
+        <v>16.05</v>
       </c>
       <c r="E74" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H74" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -2961,27 +2965,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>16.05</v>
+        <v>16.29</v>
       </c>
       <c r="E75" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -3000,14 +3000,14 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>16.27</v>
+        <v>16.51</v>
       </c>
       <c r="E76" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -3031,14 +3031,14 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>16.51</v>
+        <v>16.27</v>
       </c>
       <c r="E77" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -3128,27 +3128,23 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>16.68</v>
+        <v>15.94</v>
       </c>
       <c r="E80" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I80" t="b">
         <v>0</v>
@@ -3163,23 +3159,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>15.94</v>
+        <v>16.68</v>
       </c>
       <c r="E81" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H81" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I81" t="b">
         <v>0</v>
@@ -3435,14 +3435,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>LCO</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>16.9</v>
+        <v>16.61</v>
       </c>
       <c r="E89" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3451,11 +3451,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>42269</v>
+        <v>422561</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
@@ -3470,14 +3470,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LCO</t>
+          <t>Osservatorio Astronomico "Nastro Verde"</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>16.61</v>
+        <v>16.9</v>
       </c>
       <c r="E90" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>422561</v>
+        <v>42269</v>
       </c>
       <c r="I90" t="b">
         <v>0</v>
@@ -3610,14 +3610,14 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>16.75</v>
+        <v>16.3</v>
       </c>
       <c r="E94" t="n">
         <v>0.02</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -3672,14 +3672,14 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>16.3</v>
+        <v>16.75</v>
       </c>
       <c r="E96" t="n">
         <v>0.02</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -3971,27 +3971,23 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>16.5</v>
+        <v>16.37</v>
       </c>
       <c r="E105" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>Rc</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>42269</v>
+        <v>42333</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
@@ -4006,23 +4002,27 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Osservatorio Astronomico "Nastro Verde"</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>16.37</v>
+        <v>16.5</v>
       </c>
       <c r="E106" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>Rc</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H106" t="n">
-        <v>42333</v>
+        <v>42269</v>
       </c>
       <c r="I106" t="b">
         <v>0</v>
@@ -4379,23 +4379,27 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Bassano Bresciano Observatory</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>16.05</v>
+        <v>16.29</v>
       </c>
       <c r="E117" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H117" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I117" t="b">
         <v>0</v>
@@ -4410,27 +4414,23 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>16.8</v>
+        <v>16.05</v>
       </c>
       <c r="E118" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
@@ -4445,14 +4445,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>16.29</v>
+        <v>16.8</v>
       </c>
       <c r="E119" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4461,11 +4461,11 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I119" t="b">
         <v>0</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -5500,27 +5500,23 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>17.02</v>
+        <v>16.54</v>
       </c>
       <c r="E150" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I150" t="b">
         <v>0</v>
@@ -5535,23 +5531,27 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>16.54</v>
+        <v>17.02</v>
       </c>
       <c r="E151" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H151" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I151" t="b">
         <v>0</v>
@@ -5663,14 +5663,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Bassano Bresciano Observatory</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>17.02</v>
+        <v>16.55</v>
       </c>
       <c r="E155" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -5679,11 +5679,11 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>42275</v>
+        <v>42262</v>
       </c>
       <c r="I155" t="b">
         <v>0</v>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>16.55</v>
+        <v>17.02</v>
       </c>
       <c r="E156" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -5714,11 +5714,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I156" t="b">
         <v>0</v>
@@ -5935,23 +5935,27 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Bassano Bresciano Observatory</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>16.8</v>
+        <v>16.61</v>
       </c>
       <c r="E163" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H163" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I163" t="b">
         <v>0</v>
@@ -5966,27 +5970,23 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>16.61</v>
+        <v>16.8</v>
       </c>
       <c r="E164" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I164" t="b">
         <v>0</v>
@@ -6665,11 +6665,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>16.83</v>
+        <v>17.31</v>
       </c>
       <c r="E185" t="n">
         <v>0.02</v>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I185" t="b">
         <v>0</v>
@@ -6700,27 +6700,23 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>17.31</v>
+        <v>17.11</v>
       </c>
       <c r="E186" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I186" t="b">
         <v>0</v>
@@ -6735,23 +6731,27 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Bassano Bresciano Observatory</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>17.11</v>
+        <v>16.83</v>
       </c>
       <c r="E187" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H187" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I187" t="b">
         <v>0</v>
@@ -6832,27 +6832,23 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t xml:space="preserve">Leavitt </t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>17.35</v>
+        <v>16.63</v>
       </c>
       <c r="E190" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I190" t="b">
         <v>0</v>
@@ -6867,23 +6863,27 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>16.63</v>
+        <v>17.35</v>
       </c>
       <c r="E191" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H191" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I191" t="b">
         <v>0</v>
@@ -7388,27 +7388,27 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MarSEC</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>17.58</v>
+        <v>17.7</v>
       </c>
       <c r="E206" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>42267</v>
+        <v>42275</v>
       </c>
       <c r="I206" t="b">
         <v>0</v>
@@ -7423,27 +7423,27 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MarSEC</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>17.7</v>
+        <v>17.58</v>
       </c>
       <c r="E207" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H207" t="n">
-        <v>42275</v>
+        <v>42267</v>
       </c>
       <c r="I207" t="b">
         <v>0</v>
@@ -7692,174 +7692,150 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>45944.00292824074</v>
+        <v>45944.00287809028</v>
       </c>
       <c r="B215" t="n">
         <v>6.41</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ISON-Castelgrande</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>17.54</v>
+        <v>17.51163935972227</v>
       </c>
       <c r="E215" t="n">
-        <v>0.19</v>
+        <v>0.6164457444803931</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>35*60</t>
-        </is>
-      </c>
-      <c r="H215" t="n">
-        <v>42396</v>
-      </c>
+          <t>m850</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
       <c r="I215" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>45944.003</v>
+        <v>45944.00288194444</v>
       </c>
       <c r="B216" t="n">
         <v>6.41</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>18.03</v>
+        <v>17.5783</v>
       </c>
       <c r="E216" t="n">
-        <v>0.05</v>
+        <v>0.079</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
-      <c r="H216" t="n">
-        <v>42275</v>
-      </c>
+          <t>m650</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>45944.00548611111</v>
+        <v>45944.00289351852</v>
       </c>
       <c r="B217" t="n">
-        <v>6.47</v>
+        <v>6.41</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Kilonova-Catcher</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>17.63</v>
+        <v>18.0339</v>
       </c>
       <c r="E217" t="n">
-        <v>0.02</v>
+        <v>0.0583</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>5x300</t>
-        </is>
-      </c>
-      <c r="H217" t="n">
-        <v>42301</v>
-      </c>
+          <t>m450</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>45944.009</v>
+        <v>45944.00291666666</v>
       </c>
       <c r="B218" t="n">
-        <v>6.55</v>
+        <v>6.41</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>17.97</v>
+        <v>17.4843</v>
       </c>
       <c r="E218" t="n">
-        <v>0.05</v>
+        <v>0.0917</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
-      <c r="H218" t="n">
-        <v>42275</v>
-      </c>
+          <t>m700</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
       <c r="I218" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>45944.015</v>
+        <v>45944.00292824074</v>
       </c>
       <c r="B219" t="n">
-        <v>6.7</v>
+        <v>6.41</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>ISON-Castelgrande</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>17.99</v>
+        <v>17.54</v>
       </c>
       <c r="E219" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>35*60</t>
         </is>
       </c>
       <c r="H219" t="n">
-        <v>42275</v>
+        <v>42396</v>
       </c>
       <c r="I219" t="b">
         <v>0</v>
@@ -7867,96 +7843,92 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>45944.022</v>
+        <v>45944.00295138889</v>
       </c>
       <c r="B220" t="n">
-        <v>6.87</v>
+        <v>6.41</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>18.06</v>
+        <v>18.091</v>
       </c>
       <c r="E220" t="n">
-        <v>0.05</v>
+        <v>0.0225</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>11x60s</t>
-        </is>
-      </c>
-      <c r="H220" t="n">
-        <v>42275</v>
-      </c>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
       <c r="I220" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>45944.07417824074</v>
+        <v>45944.00298611111</v>
       </c>
       <c r="B221" t="n">
-        <v>8.119999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>18.62</v>
+        <v>17.6587</v>
       </c>
       <c r="E221" t="n">
-        <v>0.04</v>
+        <v>0.1052</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>m625</t>
         </is>
       </c>
       <c r="G221" t="inlineStr"/>
-      <c r="H221" t="n">
-        <v>42334</v>
-      </c>
+      <c r="H221" t="inlineStr"/>
       <c r="I221" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>45944.07517361111</v>
+        <v>45944.003</v>
       </c>
       <c r="B222" t="n">
-        <v>8.140000000000001</v>
+        <v>6.41</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>18.36</v>
+        <v>18.03</v>
       </c>
       <c r="E222" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H222" t="n">
-        <v>42334</v>
+        <v>42275</v>
       </c>
       <c r="I222" t="b">
         <v>0</v>
@@ -7964,21 +7936,21 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>45944.07613425926</v>
+        <v>45944.00303240741</v>
       </c>
       <c r="B223" t="n">
-        <v>8.17</v>
+        <v>6.41</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>18.14</v>
+        <v>17.3029</v>
       </c>
       <c r="E223" t="n">
-        <v>0.03</v>
+        <v>0.0659</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -7986,175 +7958,157 @@
         </is>
       </c>
       <c r="G223" t="inlineStr"/>
-      <c r="H223" t="n">
-        <v>42334</v>
-      </c>
+      <c r="H223" t="inlineStr"/>
       <c r="I223" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>45944.07710648148</v>
+        <v>45944.00310185185</v>
       </c>
       <c r="B224" t="n">
-        <v>8.19</v>
+        <v>6.41</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>19.07</v>
+        <v>16.95181064496047</v>
       </c>
       <c r="E224" t="n">
-        <v>0.1</v>
+        <v>0.2110187522250844</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>m800</t>
         </is>
       </c>
       <c r="G224" t="inlineStr"/>
-      <c r="H224" t="n">
-        <v>42334</v>
-      </c>
+      <c r="H224" t="inlineStr"/>
       <c r="I224" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>45944.07877314815</v>
+        <v>45944.00310185185</v>
       </c>
       <c r="B225" t="n">
-        <v>8.23</v>
+        <v>6.41</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>18</v>
+        <v>17.8604</v>
       </c>
       <c r="E225" t="n">
-        <v>0.03</v>
+        <v>0.1003</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>m600</t>
         </is>
       </c>
       <c r="G225" t="inlineStr"/>
-      <c r="H225" t="n">
-        <v>42334</v>
-      </c>
+      <c r="H225" t="inlineStr"/>
       <c r="I225" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>45944.08006944445</v>
+        <v>45944.00314814815</v>
       </c>
       <c r="B226" t="n">
-        <v>8.26</v>
+        <v>6.41</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Kilonova-Catcher</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>18.24</v>
+        <v>17.8886</v>
       </c>
       <c r="E226" t="n">
-        <v>0.05</v>
+        <v>0.0701</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6x300 </t>
-        </is>
-      </c>
-      <c r="H226" t="n">
-        <v>42301</v>
-      </c>
+          <t>m575</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
       <c r="I226" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>45944.09583333333</v>
+        <v>45944.00530285879</v>
       </c>
       <c r="B227" t="n">
-        <v>8.640000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SVOM/COLIBRÍ (FM-GFT)</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>18.5</v>
+        <v>16.88992912508132</v>
       </c>
       <c r="E227" t="n">
-        <v>0.03</v>
+        <v>0.4916548577615109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H227" t="n">
-        <v>42242</v>
-      </c>
+          <t>m875</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>45944.11180555556</v>
+        <v>45944.00548611111</v>
       </c>
       <c r="B228" t="n">
-        <v>9.02</v>
+        <v>6.47</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DDOTI</t>
+          <t>Kilonova-Catcher</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>18.95</v>
+        <v>17.63</v>
       </c>
       <c r="E228" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>5x300</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>42241</v>
+        <v>42301</v>
       </c>
       <c r="I228" t="b">
         <v>0</v>
@@ -8162,407 +8116,353 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>45944.514</v>
+        <v>45944.00555362269</v>
       </c>
       <c r="B229" t="n">
-        <v>18.67</v>
+        <v>6.47</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>LCO</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>20.73</v>
+        <v>17.2918</v>
       </c>
       <c r="E229" t="n">
-        <v>0.05</v>
+        <v>0.1273</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="H229" t="n">
-        <v>422561</v>
-      </c>
+          <t>m750</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
       <c r="I229" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>45944.7325</v>
+        <v>45944.00767361111</v>
       </c>
       <c r="B230" t="n">
-        <v>23.92</v>
+        <v>6.52</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>MAO/AZT-22</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>20.96</v>
+        <v>17.30872064963861</v>
       </c>
       <c r="E230" t="n">
-        <v>0.04</v>
+        <v>0.2275235299181369</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6x300 </t>
-        </is>
-      </c>
-      <c r="H230" t="n">
-        <v>42283</v>
-      </c>
+          <t>m775</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>45944.89798611111</v>
+        <v>45944.00772762732</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89</v>
+        <v>6.52</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>OHP/T193</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>21.11</v>
+        <v>18.0455</v>
       </c>
       <c r="E231" t="n">
-        <v>0.1</v>
+        <v>0.0552</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>g'</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>3x600 + 1x300</t>
-        </is>
-      </c>
-      <c r="H231" t="n">
-        <v>42276</v>
-      </c>
+          <t>m475</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
       <c r="I231" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>45944.93215277778</v>
+        <v>45944.00773148148</v>
       </c>
       <c r="B232" t="n">
-        <v>28.71</v>
+        <v>6.52</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>OHP/T193</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>21.29</v>
+        <v>18.6177</v>
       </c>
       <c r="E232" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1533</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>r'</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>2x600 + 1x900</t>
-        </is>
-      </c>
-      <c r="H232" t="n">
-        <v>42276</v>
-      </c>
+          <t>m400</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
       <c r="I232" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>45945.12222222222</v>
+        <v>45944.00774305555</v>
       </c>
       <c r="B233" t="n">
-        <v>33.27</v>
+        <v>6.52</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVOM/COLIBRÍ </t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>21.59</v>
+        <v>17.8869</v>
       </c>
       <c r="E233" t="n">
-        <v>0.04</v>
+        <v>0.0483</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="H233" t="n">
-        <v>42279</v>
-      </c>
+          <t>m525</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
       <c r="I233" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>45945.12222222222</v>
+        <v>45944.00778935185</v>
       </c>
       <c r="B234" t="n">
-        <v>33.27</v>
+        <v>6.53</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVOM/COLIBRÍ </t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>21.29</v>
+        <v>17.8274</v>
       </c>
       <c r="E234" t="n">
-        <v>0.04</v>
+        <v>0.0374</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="H234" t="n">
-        <v>42279</v>
-      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>45945.12222222222</v>
+        <v>45944.00780864583</v>
       </c>
       <c r="B235" t="n">
-        <v>33.27</v>
+        <v>6.53</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVOM/COLIBRÍ </t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>20.93</v>
+        <v>17.8523</v>
       </c>
       <c r="E235" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>z</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>3840</t>
-        </is>
-      </c>
-      <c r="H235" t="n">
-        <v>42279</v>
-      </c>
+          <t>m550</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
       <c r="I235" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>45945.23857638889</v>
+        <v>45944.0078125</v>
       </c>
       <c r="B236" t="n">
-        <v>36.06</v>
+        <v>6.53</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Swift/UVOT</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>21.66</v>
+        <v>18.2558</v>
       </c>
       <c r="E236" t="n">
-        <v>0.2</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>white</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="H236" t="n">
-        <v>42298</v>
-      </c>
+          <t>m425</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
       <c r="I236" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>45945.73431712963</v>
+        <v>45944.00810185185</v>
       </c>
       <c r="B237" t="n">
-        <v>47.96</v>
+        <v>6.53</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Koshka/Ziess-1000</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>21.5</v>
+        <v>17.51655798891263</v>
       </c>
       <c r="E237" t="n">
-        <v>0</v>
+        <v>0.3527597315123148</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>116*90</t>
-        </is>
-      </c>
-      <c r="H237" t="n">
-        <v>42736</v>
-      </c>
+          <t>m825</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
       <c r="I237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>45945.90590277778</v>
+        <v>45944.00811342592</v>
       </c>
       <c r="B238" t="n">
-        <v>52.08</v>
+        <v>6.53</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>INO340</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>22.44</v>
+        <v>17.6936</v>
       </c>
       <c r="E238" t="n">
-        <v>0.16</v>
+        <v>0.0837</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>m675</t>
         </is>
       </c>
       <c r="G238" t="inlineStr"/>
-      <c r="H238" t="n">
-        <v>42492</v>
-      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>45945.90590277778</v>
+        <v>45944.00824074074</v>
       </c>
       <c r="B239" t="n">
-        <v>52.08</v>
+        <v>6.54</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>INO340</t>
+          <t>7DT</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>21.99</v>
+        <v>18.2531</v>
       </c>
       <c r="E239" t="n">
-        <v>0.25</v>
+        <v>0.0623</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>m500</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
-      <c r="H239" t="n">
-        <v>42492</v>
-      </c>
+      <c r="H239" t="inlineStr"/>
       <c r="I239" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>45945.90590277778</v>
+        <v>45944.009</v>
       </c>
       <c r="B240" t="n">
-        <v>52.08</v>
+        <v>6.55</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>INO340</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>21.61</v>
+        <v>17.97</v>
       </c>
       <c r="E240" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H240" t="n">
-        <v>42492</v>
+        <v>42275</v>
       </c>
       <c r="I240" t="b">
         <v>0</v>
@@ -8570,30 +8470,34 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>45946.5578125</v>
+        <v>45944.015</v>
       </c>
       <c r="B241" t="n">
-        <v>67.73</v>
+        <v>6.7</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">JinShan </t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>21.04</v>
+        <v>17.99</v>
       </c>
       <c r="E241" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H241" t="n">
-        <v>42319</v>
+        <v>42275</v>
       </c>
       <c r="I241" t="b">
         <v>0</v>
@@ -8601,34 +8505,34 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>45947.70814814815</v>
+        <v>45944.022</v>
       </c>
       <c r="B242" t="n">
-        <v>95.33</v>
+        <v>6.87</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SAO/Zeiss-1000</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>20.41</v>
+        <v>18.06</v>
       </c>
       <c r="E242" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>10*300</t>
+          <t>11x60s</t>
         </is>
       </c>
       <c r="H242" t="n">
-        <v>42736</v>
+        <v>42275</v>
       </c>
       <c r="I242" t="b">
         <v>0</v>
@@ -8636,34 +8540,30 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>45947.79552083334</v>
+        <v>45944.07417824074</v>
       </c>
       <c r="B243" t="n">
-        <v>97.43000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>OHP/T193</t>
+          <t>Liverpool Telescope</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>20.74</v>
+        <v>18.62</v>
       </c>
       <c r="E243" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>r'</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>4x600</t>
-        </is>
-      </c>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="n">
-        <v>42338</v>
+        <v>42334</v>
       </c>
       <c r="I243" t="b">
         <v>0</v>
@@ -8671,34 +8571,30 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>45948.61255787037</v>
+        <v>45944.07517361111</v>
       </c>
       <c r="B244" t="n">
-        <v>117.04</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t>Liverpool Telescope</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>20.82</v>
+        <v>18.36</v>
       </c>
       <c r="E244" t="n">
-        <v>0.15</v>
+        <v>0.02</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>2*120</t>
-        </is>
-      </c>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="n">
-        <v>42736</v>
+        <v>42334</v>
       </c>
       <c r="I244" t="b">
         <v>0</v>
@@ -8706,34 +8602,30 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>45948.78799768518</v>
+        <v>45944.07613425926</v>
       </c>
       <c r="B245" t="n">
-        <v>121.25</v>
+        <v>8.17</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SAO/Zeiss-1000</t>
+          <t>Liverpool Telescope</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>21.02</v>
+        <v>18.14</v>
       </c>
       <c r="E245" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>10*300</t>
-        </is>
-      </c>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="n">
-        <v>42736</v>
+        <v>42334</v>
       </c>
       <c r="I245" t="b">
         <v>0</v>
@@ -8741,34 +8633,30 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>45949.52506944445</v>
+        <v>45944.07710648148</v>
       </c>
       <c r="B246" t="n">
-        <v>138.94</v>
+        <v>8.19</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t>Liverpool Telescope</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>21.58</v>
+        <v>19.07</v>
       </c>
       <c r="E246" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>35*120</t>
-        </is>
-      </c>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="n">
-        <v>42736</v>
+        <v>42334</v>
       </c>
       <c r="I246" t="b">
         <v>0</v>
@@ -8776,34 +8664,30 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>45950.78024305555</v>
+        <v>45944.07877314815</v>
       </c>
       <c r="B247" t="n">
-        <v>169.06</v>
+        <v>8.23</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Koshka/Ziess-1000</t>
+          <t>Liverpool Telescope</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>20.7</v>
+        <v>18</v>
       </c>
       <c r="E247" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>40*180</t>
-        </is>
-      </c>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="n">
-        <v>42736</v>
+        <v>42334</v>
       </c>
       <c r="I247" t="b">
         <v>0</v>
@@ -8811,34 +8695,34 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>45950.8330787037</v>
+        <v>45944.08006944445</v>
       </c>
       <c r="B248" t="n">
-        <v>170.33</v>
+        <v>8.26</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>SAO RAS</t>
+          <t>Kilonova-Catcher</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>21.61</v>
+        <v>18.24</v>
       </c>
       <c r="E248" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>13x300</t>
+          <t xml:space="preserve">6x300 </t>
         </is>
       </c>
       <c r="H248" t="n">
-        <v>42399</v>
+        <v>42301</v>
       </c>
       <c r="I248" t="b">
         <v>0</v>
@@ -8846,34 +8730,34 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>45950.8330787037</v>
+        <v>45944.09583333333</v>
       </c>
       <c r="B249" t="n">
-        <v>170.33</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>SAO/Zeiss-1000</t>
+          <t>SVOM/COLIBRÍ (FM-GFT)</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>21.61</v>
+        <v>18.5</v>
       </c>
       <c r="E249" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>13*300</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H249" t="n">
-        <v>42736</v>
+        <v>42242</v>
       </c>
       <c r="I249" t="b">
         <v>0</v>
@@ -8881,34 +8765,34 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>45951.52146990741</v>
+        <v>45944.11180555556</v>
       </c>
       <c r="B250" t="n">
-        <v>186.85</v>
+        <v>9.02</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t>DDOTI</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>21.89</v>
+        <v>18.95</v>
       </c>
       <c r="E250" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>w</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>40*120</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="H250" t="n">
-        <v>42736</v>
+        <v>42241</v>
       </c>
       <c r="I250" t="b">
         <v>0</v>
@@ -8916,34 +8800,34 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>45951.71008101852</v>
+        <v>45944.514</v>
       </c>
       <c r="B251" t="n">
-        <v>191.38</v>
+        <v>18.67</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>SAO RAS</t>
+          <t>LCO</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>21.8</v>
+        <v>20.73</v>
       </c>
       <c r="E251" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>19x300</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H251" t="n">
-        <v>42399</v>
+        <v>422561</v>
       </c>
       <c r="I251" t="b">
         <v>0</v>
@@ -8951,21 +8835,21 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>45952.52082175926</v>
+        <v>45944.7325</v>
       </c>
       <c r="B252" t="n">
-        <v>210.84</v>
+        <v>23.92</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t>MAO/AZT-22</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>21.63</v>
+        <v>20.96</v>
       </c>
       <c r="E252" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -8974,11 +8858,11 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>37*120</t>
+          <t xml:space="preserve">6x300 </t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>42736</v>
+        <v>42283</v>
       </c>
       <c r="I252" t="b">
         <v>0</v>
@@ -8986,34 +8870,34 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>45953.5036574074</v>
+        <v>45944.89798611111</v>
       </c>
       <c r="B253" t="n">
-        <v>234.43</v>
+        <v>27.89</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t>OHP/T193</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>22.31</v>
+        <v>21.11</v>
       </c>
       <c r="E253" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>g'</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>35*120</t>
+          <t>3x600 + 1x300</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>42736</v>
+        <v>42276</v>
       </c>
       <c r="I253" t="b">
         <v>0</v>
@@ -9021,34 +8905,34 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>45953.80598379629</v>
+        <v>45944.93215277778</v>
       </c>
       <c r="B254" t="n">
-        <v>241.68</v>
+        <v>28.71</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SAO/Zeiss-1000</t>
+          <t>OHP/T193</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>22.31</v>
+        <v>21.29</v>
       </c>
       <c r="E254" t="n">
-        <v>0.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>r'</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>6*300</t>
+          <t>2x600 + 1x900</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>42736</v>
+        <v>42276</v>
       </c>
       <c r="I254" t="b">
         <v>0</v>
@@ -9056,69 +8940,69 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>45954.78755787037</v>
+        <v>45945.12222222222</v>
       </c>
       <c r="B255" t="n">
-        <v>265.24</v>
+        <v>33.27</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SAO/Zeiss-1000</t>
+          <t xml:space="preserve">SVOM/COLIBRÍ </t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>22</v>
+        <v>20.93</v>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>z</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>6*300</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="H255" t="n">
-        <v>42736</v>
+        <v>42279</v>
       </c>
       <c r="I255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>45955.67466435185</v>
+        <v>45945.12222222222</v>
       </c>
       <c r="B256" t="n">
-        <v>286.53</v>
+        <v>33.27</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>CrAO/ZTSh</t>
+          <t xml:space="preserve">SVOM/COLIBRÍ </t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>21.7</v>
+        <v>21.29</v>
       </c>
       <c r="E256" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>38*120</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>42736</v>
+        <v>42279</v>
       </c>
       <c r="I256" t="b">
         <v>0</v>
@@ -9126,34 +9010,34 @@
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>45956.56517361111</v>
+        <v>45945.12222222222</v>
       </c>
       <c r="B257" t="n">
-        <v>307.9</v>
+        <v>33.27</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t xml:space="preserve">SVOM/COLIBRÍ </t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>21.7</v>
+        <v>21.59</v>
       </c>
       <c r="E257" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>45*120</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>42736</v>
+        <v>42279</v>
       </c>
       <c r="I257" t="b">
         <v>0</v>
@@ -9161,34 +9045,34 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>45957.51582175926</v>
+        <v>45945.23857638889</v>
       </c>
       <c r="B258" t="n">
-        <v>330.72</v>
+        <v>36.06</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t>Swift/UVOT</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>22.13</v>
+        <v>21.66</v>
       </c>
       <c r="E258" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>white</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>45*120</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>42736</v>
+        <v>42298</v>
       </c>
       <c r="I258" t="b">
         <v>0</v>
@@ -9196,21 +9080,21 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>45958.52263888889</v>
+        <v>45945.73431712963</v>
       </c>
       <c r="B259" t="n">
-        <v>354.88</v>
+        <v>47.96</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Mondy/AZT-33IK</t>
+          <t>Koshka/Ziess-1000</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>22.23</v>
+        <v>21.5</v>
       </c>
       <c r="E259" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -9219,48 +9103,802 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>44*120</t>
+          <t>116*90</t>
         </is>
       </c>
       <c r="H259" t="n">
         <v>42736</v>
       </c>
       <c r="I259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
+        <v>45945.90590277778</v>
+      </c>
+      <c r="B260" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>INO340</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="n">
+        <v>42492</v>
+      </c>
+      <c r="I260" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>45945.90590277778</v>
+      </c>
+      <c r="B261" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>INO340</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="n">
+        <v>42492</v>
+      </c>
+      <c r="I261" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>45945.90590277778</v>
+      </c>
+      <c r="B262" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>INO340</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="n">
+        <v>42492</v>
+      </c>
+      <c r="I262" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>45946.5578125</v>
+      </c>
+      <c r="B263" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JinShan </t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="n">
+        <v>42319</v>
+      </c>
+      <c r="I263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>45947.70814814815</v>
+      </c>
+      <c r="B264" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SAO/Zeiss-1000</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>10*300</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>45947.79552083334</v>
+      </c>
+      <c r="B265" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>OHP/T193</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>r'</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>4x600</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>42338</v>
+      </c>
+      <c r="I265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>45948.61255787037</v>
+      </c>
+      <c r="B266" t="n">
+        <v>117.04</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2*120</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>45948.78799768518</v>
+      </c>
+      <c r="B267" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SAO/Zeiss-1000</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>10*300</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>45949.52506944445</v>
+      </c>
+      <c r="B268" t="n">
+        <v>138.94</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>35*120</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>45950.78024305555</v>
+      </c>
+      <c r="B269" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Koshka/Ziess-1000</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>40*180</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I269" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>45950.8330787037</v>
+      </c>
+      <c r="B270" t="n">
+        <v>170.33</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SAO RAS</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>13x300</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>42399</v>
+      </c>
+      <c r="I270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>45950.8330787037</v>
+      </c>
+      <c r="B271" t="n">
+        <v>170.33</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SAO/Zeiss-1000</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>13*300</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>45951.52146990741</v>
+      </c>
+      <c r="B272" t="n">
+        <v>186.85</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>40*120</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I272" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>45951.71008101852</v>
+      </c>
+      <c r="B273" t="n">
+        <v>191.38</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SAO RAS</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>19x300</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>42399</v>
+      </c>
+      <c r="I273" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>45952.52082175926</v>
+      </c>
+      <c r="B274" t="n">
+        <v>210.84</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>37*120</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I274" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>45953.5036574074</v>
+      </c>
+      <c r="B275" t="n">
+        <v>234.43</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>35*120</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I275" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>45953.80598379629</v>
+      </c>
+      <c r="B276" t="n">
+        <v>241.68</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SAO/Zeiss-1000</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>6*300</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I276" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>45954.78755787037</v>
+      </c>
+      <c r="B277" t="n">
+        <v>265.24</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SAO/Zeiss-1000</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>22</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>6*300</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I277" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>45955.67466435185</v>
+      </c>
+      <c r="B278" t="n">
+        <v>286.53</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>CrAO/ZTSh</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>38*120</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I278" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>45956.56517361111</v>
+      </c>
+      <c r="B279" t="n">
+        <v>307.9</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>45*120</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I279" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>45957.51582175926</v>
+      </c>
+      <c r="B280" t="n">
+        <v>330.72</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>45*120</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>45958.52263888889</v>
+      </c>
+      <c r="B281" t="n">
+        <v>354.88</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Mondy/AZT-33IK</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>44*120</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>42736</v>
+      </c>
+      <c r="I281" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
         <v>45958.81748842593</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B282" t="n">
         <v>361.96</v>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>SAO/Zeiss-1000</t>
         </is>
       </c>
-      <c r="D260" t="n">
+      <c r="D282" t="n">
         <v>22.46</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E282" t="n">
         <v>0.22</v>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>Rc</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G282" t="inlineStr">
         <is>
           <t>10*300</t>
         </is>
       </c>
-      <c r="H260" t="n">
+      <c r="H282" t="n">
         <v>42736</v>
       </c>
-      <c r="I260" t="b">
+      <c r="I282" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/circular.xlsx
+++ b/data/circular.xlsx
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SAO RAS</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAO RAS</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAO RAS</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Osservatorio Astronomico "Nastro Verde"</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASTER-SAAO </t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leavitt </t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bassano Bresciano Observatory</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>LiverpoolTelescope</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>LiverpoolTelescope</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>LiverpoolTelescope</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>LiverpoolTelescope</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Liverpool Telescope</t>
+          <t>LiverpoolTelescope</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>SVOM/COLIBRÍ (FM-GFT)</t>
+          <t>SVOM/COLIBRÍ(FM-GFT)</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVOM/COLIBRÍ </t>
+          <t>SVOM/COLIBRÍ</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVOM/COLIBRÍ </t>
+          <t>SVOM/COLIBRÍ</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVOM/COLIBRÍ </t>
+          <t>SVOM/COLIBRÍ</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">JinShan </t>
+          <t>JinShan</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAO RAS</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>SAO RAS</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D273" t="n">

--- a/data/circular.xlsx
+++ b/data/circular.xlsx
@@ -435,37 +435,37 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Starting Date</t>
+          <t>date_obs</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Mag</t>
+          <t>magnitude</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>mag_error</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Exposure</t>
+          <t>exposure</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>upper_limit</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
         <v>45943.73701388889</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03</v>
+        <v>96</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
         <v>45943.73732638889</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03</v>
+        <v>123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         <v>45943.73753472222</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04</v>
+        <v>141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>45943.73804398148</v>
       </c>
       <c r="B5" t="n">
-        <v>0.05</v>
+        <v>185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         <v>45943.7382175926</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06</v>
+        <v>200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45943.73873842593</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07000000000000001</v>
+        <v>245</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         <v>45943.73893518518</v>
       </c>
       <c r="B8" t="n">
-        <v>0.07000000000000001</v>
+        <v>262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45943.73893518518</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07000000000000001</v>
+        <v>262</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>45943.73924768518</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08</v>
+        <v>289</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>45943.73943287037</v>
       </c>
       <c r="B11" t="n">
-        <v>0.08</v>
+        <v>305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45943.74082175926</v>
       </c>
       <c r="B12" t="n">
-        <v>0.12</v>
+        <v>425</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45943.74145833333</v>
       </c>
       <c r="B13" t="n">
-        <v>0.13</v>
+        <v>480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>45943.74325231482</v>
       </c>
       <c r="B14" t="n">
-        <v>0.18</v>
+        <v>635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45943.74332175926</v>
       </c>
       <c r="B15" t="n">
-        <v>0.18</v>
+        <v>641</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>45943.74435185185</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2</v>
+        <v>730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45943.74842592593</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3</v>
+        <v>1082</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45943.74945601852</v>
       </c>
       <c r="B18" t="n">
-        <v>0.33</v>
+        <v>1171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45943.75256944444</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4</v>
+        <v>1440</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45943.75351851852</v>
       </c>
       <c r="B20" t="n">
-        <v>0.42</v>
+        <v>1522</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45943.75725694445</v>
       </c>
       <c r="B21" t="n">
-        <v>0.51</v>
+        <v>1845</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45943.76805555556</v>
       </c>
       <c r="B22" t="n">
-        <v>0.77</v>
+        <v>2778</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45943.76895833333</v>
       </c>
       <c r="B23" t="n">
-        <v>0.79</v>
+        <v>2856</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45943.77239583333</v>
       </c>
       <c r="B24" t="n">
-        <v>0.88</v>
+        <v>3153</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45943.795</v>
       </c>
       <c r="B25" t="n">
-        <v>1.42</v>
+        <v>5106</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45943.801</v>
       </c>
       <c r="B26" t="n">
-        <v>1.56</v>
+        <v>5624.4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45943.804</v>
       </c>
       <c r="B27" t="n">
-        <v>1.63</v>
+        <v>5883.6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>45943.807</v>
       </c>
       <c r="B28" t="n">
-        <v>1.71</v>
+        <v>6142.8</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45943.807</v>
       </c>
       <c r="B29" t="n">
-        <v>1.71</v>
+        <v>6142.8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>45943.81</v>
       </c>
       <c r="B30" t="n">
-        <v>1.78</v>
+        <v>6402</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45943.81090277778</v>
       </c>
       <c r="B31" t="n">
-        <v>1.8</v>
+        <v>6480</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45943.81155092592</v>
       </c>
       <c r="B32" t="n">
-        <v>1.82</v>
+        <v>6536</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>45943.813</v>
       </c>
       <c r="B33" t="n">
-        <v>1.85</v>
+        <v>6661.2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45943.813</v>
       </c>
       <c r="B34" t="n">
-        <v>1.85</v>
+        <v>6661.2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45943.816</v>
       </c>
       <c r="B35" t="n">
-        <v>1.92</v>
+        <v>6920.4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45943.818</v>
       </c>
       <c r="B36" t="n">
-        <v>1.97</v>
+        <v>7093.2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45943.818</v>
       </c>
       <c r="B37" t="n">
-        <v>1.97</v>
+        <v>7093.2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45943.819</v>
       </c>
       <c r="B38" t="n">
-        <v>1.99</v>
+        <v>7179.6</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45943.819</v>
       </c>
       <c r="B39" t="n">
-        <v>1.99</v>
+        <v>7179.6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>45943.81923611111</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>7200</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45943.82</v>
       </c>
       <c r="B41" t="n">
-        <v>2.02</v>
+        <v>7266</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45943.822</v>
       </c>
       <c r="B42" t="n">
-        <v>2.07</v>
+        <v>7438.8</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45943.822</v>
       </c>
       <c r="B43" t="n">
-        <v>2.07</v>
+        <v>7438.8</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45943.82340277778</v>
       </c>
       <c r="B44" t="n">
-        <v>2.1</v>
+        <v>7560</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45943.824</v>
       </c>
       <c r="B45" t="n">
-        <v>2.11</v>
+        <v>7611.6</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45943.824</v>
       </c>
       <c r="B46" t="n">
-        <v>2.11</v>
+        <v>7611.6</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>45943.82493055556</v>
       </c>
       <c r="B47" t="n">
-        <v>2.14</v>
+        <v>7692</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45943.826</v>
       </c>
       <c r="B48" t="n">
-        <v>2.16</v>
+        <v>7784.4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45943.827</v>
       </c>
       <c r="B49" t="n">
-        <v>2.19</v>
+        <v>7870.8</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>45943.829</v>
       </c>
       <c r="B50" t="n">
-        <v>2.23</v>
+        <v>8043.6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45943.83</v>
       </c>
       <c r="B51" t="n">
-        <v>2.26</v>
+        <v>8130</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>45943.83</v>
       </c>
       <c r="B52" t="n">
-        <v>2.26</v>
+        <v>8130</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45943.831</v>
       </c>
       <c r="B53" t="n">
-        <v>2.28</v>
+        <v>8216.4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45943.833</v>
       </c>
       <c r="B54" t="n">
-        <v>2.33</v>
+        <v>8389.200000000001</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45943.833</v>
       </c>
       <c r="B55" t="n">
-        <v>2.33</v>
+        <v>8389.200000000001</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45943.835</v>
       </c>
       <c r="B56" t="n">
-        <v>2.38</v>
+        <v>8562</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45943.836</v>
       </c>
       <c r="B57" t="n">
-        <v>2.4</v>
+        <v>8648.4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45943.83613425926</v>
       </c>
       <c r="B58" t="n">
-        <v>2.41</v>
+        <v>8660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45943.837</v>
       </c>
       <c r="B59" t="n">
-        <v>2.43</v>
+        <v>8734.799999999999</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45943.837</v>
       </c>
       <c r="B60" t="n">
-        <v>2.43</v>
+        <v>8734.799999999999</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45943.837</v>
       </c>
       <c r="B61" t="n">
-        <v>2.43</v>
+        <v>8734.799999999999</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45943.837</v>
       </c>
       <c r="B62" t="n">
-        <v>2.43</v>
+        <v>8734.799999999999</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45943.839</v>
       </c>
       <c r="B63" t="n">
-        <v>2.47</v>
+        <v>8907.6</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45943.84</v>
       </c>
       <c r="B64" t="n">
-        <v>2.5</v>
+        <v>8994</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45943.841</v>
       </c>
       <c r="B65" t="n">
-        <v>2.52</v>
+        <v>9080.4</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45943.841</v>
       </c>
       <c r="B66" t="n">
-        <v>2.52</v>
+        <v>9080.4</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45943.843</v>
       </c>
       <c r="B67" t="n">
-        <v>2.57</v>
+        <v>9253.200000000001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>45943.844</v>
       </c>
       <c r="B68" t="n">
-        <v>2.59</v>
+        <v>9339.6</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45943.84414351852</v>
       </c>
       <c r="B69" t="n">
-        <v>2.6</v>
+        <v>9352</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>45943.845</v>
       </c>
       <c r="B70" t="n">
-        <v>2.62</v>
+        <v>9426</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>45943.846</v>
       </c>
       <c r="B71" t="n">
-        <v>2.64</v>
+        <v>9512.4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45943.847</v>
       </c>
       <c r="B72" t="n">
-        <v>2.67</v>
+        <v>9598.799999999999</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45943.847</v>
       </c>
       <c r="B73" t="n">
-        <v>2.67</v>
+        <v>9598.799999999999</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45943.848</v>
       </c>
       <c r="B74" t="n">
-        <v>2.69</v>
+        <v>9685.200000000001</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45943.848</v>
       </c>
       <c r="B75" t="n">
-        <v>2.69</v>
+        <v>9685.200000000001</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45943.85048611111</v>
       </c>
       <c r="B76" t="n">
-        <v>2.75</v>
+        <v>9900</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>45943.85048611111</v>
       </c>
       <c r="B77" t="n">
-        <v>2.75</v>
+        <v>9900</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45943.851</v>
       </c>
       <c r="B78" t="n">
-        <v>2.76</v>
+        <v>9944.4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45943.85203703704</v>
       </c>
       <c r="B79" t="n">
-        <v>2.79</v>
+        <v>10034</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45943.853</v>
       </c>
       <c r="B80" t="n">
-        <v>2.81</v>
+        <v>10117.2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>45943.853</v>
       </c>
       <c r="B81" t="n">
-        <v>2.81</v>
+        <v>10117.2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45943.85311342592</v>
       </c>
       <c r="B82" t="n">
-        <v>2.81</v>
+        <v>10127</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45943.85418981482</v>
       </c>
       <c r="B83" t="n">
-        <v>2.84</v>
+        <v>10220</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45943.855</v>
       </c>
       <c r="B84" t="n">
-        <v>2.86</v>
+        <v>10290</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>45943.855</v>
       </c>
       <c r="B85" t="n">
-        <v>2.86</v>
+        <v>10290</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>45943.855</v>
       </c>
       <c r="B86" t="n">
-        <v>2.86</v>
+        <v>10290</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>45943.85528935185</v>
       </c>
       <c r="B87" t="n">
-        <v>2.87</v>
+        <v>10315</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>45943.85590277778</v>
       </c>
       <c r="B88" t="n">
-        <v>2.88</v>
+        <v>10368</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45943.856</v>
       </c>
       <c r="B89" t="n">
-        <v>2.88</v>
+        <v>10376.4</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45943.856</v>
       </c>
       <c r="B90" t="n">
-        <v>2.88</v>
+        <v>10376.4</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>45943.85638888889</v>
       </c>
       <c r="B91" t="n">
-        <v>2.89</v>
+        <v>10410</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45943.857</v>
       </c>
       <c r="B92" t="n">
-        <v>2.91</v>
+        <v>10462.8</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45943.85752314814</v>
       </c>
       <c r="B93" t="n">
-        <v>2.92</v>
+        <v>10508</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45943.85856481481</v>
       </c>
       <c r="B94" t="n">
-        <v>2.94</v>
+        <v>10598</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45943.85856481481</v>
       </c>
       <c r="B95" t="n">
-        <v>2.94</v>
+        <v>10598</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45943.85856481481</v>
       </c>
       <c r="B96" t="n">
-        <v>2.94</v>
+        <v>10598</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45943.85862268518</v>
       </c>
       <c r="B97" t="n">
-        <v>2.95</v>
+        <v>10603</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45943.859</v>
       </c>
       <c r="B98" t="n">
-        <v>2.95</v>
+        <v>10635.6</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45943.859</v>
       </c>
       <c r="B99" t="n">
-        <v>2.95</v>
+        <v>10635.6</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45943.859</v>
       </c>
       <c r="B100" t="n">
-        <v>2.95</v>
+        <v>10635.6</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45943.86039351852</v>
       </c>
       <c r="B101" t="n">
-        <v>2.99</v>
+        <v>10756</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>45943.861</v>
       </c>
       <c r="B102" t="n">
-        <v>3</v>
+        <v>10808.4</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45943.862</v>
       </c>
       <c r="B103" t="n">
-        <v>3.03</v>
+        <v>10894.8</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>45943.86229166666</v>
       </c>
       <c r="B104" t="n">
-        <v>3.03</v>
+        <v>10920</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45943.864</v>
       </c>
       <c r="B105" t="n">
-        <v>3.07</v>
+        <v>11067.6</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45943.864</v>
       </c>
       <c r="B106" t="n">
-        <v>3.07</v>
+        <v>11067.6</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45943.86408564815</v>
       </c>
       <c r="B107" t="n">
-        <v>3.08</v>
+        <v>11075</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45943.865</v>
       </c>
       <c r="B108" t="n">
-        <v>3.1</v>
+        <v>11154</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45943.865</v>
       </c>
       <c r="B109" t="n">
-        <v>3.1</v>
+        <v>11154</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>45943.86590277778</v>
       </c>
       <c r="B110" t="n">
-        <v>3.12</v>
+        <v>11232</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45943.866</v>
       </c>
       <c r="B111" t="n">
-        <v>3.12</v>
+        <v>11240.4</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45943.866</v>
       </c>
       <c r="B112" t="n">
-        <v>3.12</v>
+        <v>11240.4</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>45943.86767361111</v>
       </c>
       <c r="B113" t="n">
-        <v>3.16</v>
+        <v>11385</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45943.868</v>
       </c>
       <c r="B114" t="n">
-        <v>3.17</v>
+        <v>11413.2</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45943.86840277778</v>
       </c>
       <c r="B115" t="n">
-        <v>3.18</v>
+        <v>11448</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45943.86945601852</v>
       </c>
       <c r="B116" t="n">
-        <v>3.21</v>
+        <v>11539</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45943.87</v>
       </c>
       <c r="B117" t="n">
-        <v>3.22</v>
+        <v>11586</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45943.87</v>
       </c>
       <c r="B118" t="n">
-        <v>3.22</v>
+        <v>11586</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>45943.87</v>
       </c>
       <c r="B119" t="n">
-        <v>3.22</v>
+        <v>11586</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>45943.87149305556</v>
       </c>
       <c r="B120" t="n">
-        <v>3.25</v>
+        <v>11715</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45943.87197916667</v>
       </c>
       <c r="B121" t="n">
-        <v>3.27</v>
+        <v>11757</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45943.872</v>
       </c>
       <c r="B122" t="n">
-        <v>3.27</v>
+        <v>11758.8</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45943.87283564815</v>
       </c>
       <c r="B123" t="n">
-        <v>3.29</v>
+        <v>11831</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45943.873</v>
       </c>
       <c r="B124" t="n">
-        <v>3.29</v>
+        <v>11845.2</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45943.874</v>
       </c>
       <c r="B125" t="n">
-        <v>3.31</v>
+        <v>11931.6</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>45943.87447916667</v>
       </c>
       <c r="B126" t="n">
-        <v>3.33</v>
+        <v>11973</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45943.876</v>
       </c>
       <c r="B127" t="n">
-        <v>3.36</v>
+        <v>12104.4</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>45943.876</v>
       </c>
       <c r="B128" t="n">
-        <v>3.36</v>
+        <v>12104.4</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>45943.87694444445</v>
       </c>
       <c r="B129" t="n">
-        <v>3.38</v>
+        <v>12186</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>45943.877</v>
       </c>
       <c r="B130" t="n">
-        <v>3.39</v>
+        <v>12190.8</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45943.87871527778</v>
       </c>
       <c r="B131" t="n">
-        <v>3.43</v>
+        <v>12339</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45943.87871527778</v>
       </c>
       <c r="B132" t="n">
-        <v>3.43</v>
+        <v>12339</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45943.88049768518</v>
       </c>
       <c r="B133" t="n">
-        <v>3.47</v>
+        <v>12493</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45943.881</v>
       </c>
       <c r="B134" t="n">
-        <v>3.48</v>
+        <v>12536.4</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45943.882</v>
       </c>
       <c r="B135" t="n">
-        <v>3.51</v>
+        <v>12622.8</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>45943.88244212963</v>
       </c>
       <c r="B136" t="n">
-        <v>3.52</v>
+        <v>12661</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45943.884</v>
       </c>
       <c r="B137" t="n">
-        <v>3.55</v>
+        <v>12795.6</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45943.88421296296</v>
       </c>
       <c r="B138" t="n">
-        <v>3.56</v>
+        <v>12814</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45943.88421296296</v>
       </c>
       <c r="B139" t="n">
-        <v>3.56</v>
+        <v>12814</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45943.88600694444</v>
       </c>
       <c r="B140" t="n">
-        <v>3.6</v>
+        <v>12969</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45943.887</v>
       </c>
       <c r="B141" t="n">
-        <v>3.63</v>
+        <v>13054.8</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45943.88791666667</v>
       </c>
       <c r="B142" t="n">
-        <v>3.65</v>
+        <v>13134</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45943.888</v>
       </c>
       <c r="B143" t="n">
-        <v>3.65</v>
+        <v>13141.2</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45943.888</v>
       </c>
       <c r="B144" t="n">
-        <v>3.65</v>
+        <v>13141.2</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45943.889</v>
       </c>
       <c r="B145" t="n">
-        <v>3.67</v>
+        <v>13227.6</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45943.8896875</v>
       </c>
       <c r="B146" t="n">
-        <v>3.69</v>
+        <v>13287</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45943.891</v>
       </c>
       <c r="B147" t="n">
-        <v>3.72</v>
+        <v>13400.4</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45943.891</v>
       </c>
       <c r="B148" t="n">
-        <v>3.72</v>
+        <v>13400.4</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45943.89148148148</v>
       </c>
       <c r="B149" t="n">
-        <v>3.73</v>
+        <v>13442</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45943.893</v>
       </c>
       <c r="B150" t="n">
-        <v>3.77</v>
+        <v>13573.2</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45943.893</v>
       </c>
       <c r="B151" t="n">
-        <v>3.77</v>
+        <v>13573.2</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45943.895</v>
       </c>
       <c r="B152" t="n">
-        <v>3.82</v>
+        <v>13746</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>45943.896</v>
       </c>
       <c r="B153" t="n">
-        <v>3.84</v>
+        <v>13832.4</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45943.898</v>
       </c>
       <c r="B154" t="n">
-        <v>3.89</v>
+        <v>14005.2</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>45943.899</v>
       </c>
       <c r="B155" t="n">
-        <v>3.91</v>
+        <v>14091.6</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45943.899</v>
       </c>
       <c r="B156" t="n">
-        <v>3.91</v>
+        <v>14091.6</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45943.9</v>
       </c>
       <c r="B157" t="n">
-        <v>3.94</v>
+        <v>14178</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45943.902</v>
       </c>
       <c r="B158" t="n">
-        <v>3.99</v>
+        <v>14350.8</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>45943.90284722222</v>
       </c>
       <c r="B159" t="n">
-        <v>4.01</v>
+        <v>14424</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>45943.90321759259</v>
       </c>
       <c r="B160" t="n">
-        <v>4.02</v>
+        <v>14456</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45943.904</v>
       </c>
       <c r="B161" t="n">
-        <v>4.03</v>
+        <v>14523.6</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>45943.905</v>
       </c>
       <c r="B162" t="n">
-        <v>4.06</v>
+        <v>14610</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45943.906</v>
       </c>
       <c r="B163" t="n">
-        <v>4.08</v>
+        <v>14696.4</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45943.906</v>
       </c>
       <c r="B164" t="n">
-        <v>4.08</v>
+        <v>14696.4</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45943.908</v>
       </c>
       <c r="B165" t="n">
-        <v>4.13</v>
+        <v>14869.2</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45943.91</v>
       </c>
       <c r="B166" t="n">
-        <v>4.18</v>
+        <v>15042</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45943.91</v>
       </c>
       <c r="B167" t="n">
-        <v>4.18</v>
+        <v>15042</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45943.911</v>
       </c>
       <c r="B168" t="n">
-        <v>4.2</v>
+        <v>15128.4</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>45943.913</v>
       </c>
       <c r="B169" t="n">
-        <v>4.25</v>
+        <v>15301.2</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45943.913</v>
       </c>
       <c r="B170" t="n">
-        <v>4.25</v>
+        <v>15301.2</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45943.91443287037</v>
       </c>
       <c r="B171" t="n">
-        <v>4.28</v>
+        <v>15425</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45943.915</v>
       </c>
       <c r="B172" t="n">
-        <v>4.3</v>
+        <v>15474</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45943.917</v>
       </c>
       <c r="B173" t="n">
-        <v>4.35</v>
+        <v>15646.8</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45943.917</v>
       </c>
       <c r="B174" t="n">
-        <v>4.35</v>
+        <v>15646.8</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45943.917</v>
       </c>
       <c r="B175" t="n">
-        <v>4.35</v>
+        <v>15646.8</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45943.919</v>
       </c>
       <c r="B176" t="n">
-        <v>4.39</v>
+        <v>15819.6</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>45943.92</v>
       </c>
       <c r="B177" t="n">
-        <v>4.42</v>
+        <v>15906</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>45943.921</v>
       </c>
       <c r="B178" t="n">
-        <v>4.44</v>
+        <v>15992.4</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45943.922</v>
       </c>
       <c r="B179" t="n">
-        <v>4.47</v>
+        <v>16078.8</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>45943.923</v>
       </c>
       <c r="B180" t="n">
-        <v>4.49</v>
+        <v>16165.2</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45943.924</v>
       </c>
       <c r="B181" t="n">
-        <v>4.51</v>
+        <v>16251.6</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45943.925</v>
       </c>
       <c r="B182" t="n">
-        <v>4.54</v>
+        <v>16338</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45943.92641203704</v>
       </c>
       <c r="B183" t="n">
-        <v>4.57</v>
+        <v>16460</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45943.92717592593</v>
       </c>
       <c r="B184" t="n">
-        <v>4.59</v>
+        <v>16526</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45943.928</v>
       </c>
       <c r="B185" t="n">
-        <v>4.61</v>
+        <v>16597.2</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>45943.928</v>
       </c>
       <c r="B186" t="n">
-        <v>4.61</v>
+        <v>16597.2</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45943.928</v>
       </c>
       <c r="B187" t="n">
-        <v>4.61</v>
+        <v>16597.2</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>45943.93</v>
       </c>
       <c r="B188" t="n">
-        <v>4.66</v>
+        <v>16770</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45943.931</v>
       </c>
       <c r="B189" t="n">
-        <v>4.68</v>
+        <v>16856.4</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45943.934</v>
       </c>
       <c r="B190" t="n">
-        <v>4.75</v>
+        <v>17115.6</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>45943.934</v>
       </c>
       <c r="B191" t="n">
-        <v>4.75</v>
+        <v>17115.6</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45943.935</v>
       </c>
       <c r="B192" t="n">
-        <v>4.78</v>
+        <v>17202</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>45943.939</v>
       </c>
       <c r="B193" t="n">
-        <v>4.87</v>
+        <v>17547.6</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>45943.94</v>
       </c>
       <c r="B194" t="n">
-        <v>4.9</v>
+        <v>17634</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45943.942</v>
       </c>
       <c r="B195" t="n">
-        <v>4.95</v>
+        <v>17806.8</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>45943.94293981481</v>
       </c>
       <c r="B196" t="n">
-        <v>4.97</v>
+        <v>17888</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45943.945</v>
       </c>
       <c r="B197" t="n">
-        <v>5.02</v>
+        <v>18066</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45943.946</v>
       </c>
       <c r="B198" t="n">
-        <v>5.04</v>
+        <v>18152.4</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45943.95</v>
       </c>
       <c r="B199" t="n">
-        <v>5.14</v>
+        <v>18498</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45943.951</v>
       </c>
       <c r="B200" t="n">
-        <v>5.16</v>
+        <v>18584.4</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45943.953</v>
       </c>
       <c r="B201" t="n">
-        <v>5.21</v>
+        <v>18757.2</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45943.957</v>
       </c>
       <c r="B202" t="n">
-        <v>5.31</v>
+        <v>19102.8</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45943.957</v>
       </c>
       <c r="B203" t="n">
-        <v>5.31</v>
+        <v>19102.8</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45943.95795138889</v>
       </c>
       <c r="B204" t="n">
-        <v>5.33</v>
+        <v>19185</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45943.963</v>
       </c>
       <c r="B205" t="n">
-        <v>5.45</v>
+        <v>19621.2</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45943.968</v>
       </c>
       <c r="B206" t="n">
-        <v>5.57</v>
+        <v>20053.2</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45943.968</v>
       </c>
       <c r="B207" t="n">
-        <v>5.57</v>
+        <v>20053.2</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45943.974</v>
       </c>
       <c r="B208" t="n">
-        <v>5.71</v>
+        <v>20571.6</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>45943.97774305556</v>
       </c>
       <c r="B209" t="n">
-        <v>5.8</v>
+        <v>20895</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45943.98</v>
       </c>
       <c r="B210" t="n">
-        <v>5.86</v>
+        <v>21090</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45943.98039351852</v>
       </c>
       <c r="B211" t="n">
-        <v>5.87</v>
+        <v>21124</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45943.986</v>
       </c>
       <c r="B212" t="n">
-        <v>6</v>
+        <v>21608.4</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45943.992</v>
       </c>
       <c r="B213" t="n">
-        <v>6.15</v>
+        <v>22126.8</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45943.997</v>
       </c>
       <c r="B214" t="n">
-        <v>6.27</v>
+        <v>22558.8</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45944.00287809028</v>
       </c>
       <c r="B215" t="n">
-        <v>6.41</v>
+        <v>23066.67</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45944.00288194444</v>
       </c>
       <c r="B216" t="n">
-        <v>6.41</v>
+        <v>23067</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>45944.00289351852</v>
       </c>
       <c r="B217" t="n">
-        <v>6.41</v>
+        <v>23068</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45944.00291666666</v>
       </c>
       <c r="B218" t="n">
-        <v>6.41</v>
+        <v>23070</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45944.00292824074</v>
       </c>
       <c r="B219" t="n">
-        <v>6.41</v>
+        <v>23071</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45944.00295138889</v>
       </c>
       <c r="B220" t="n">
-        <v>6.41</v>
+        <v>23073</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45944.00298611111</v>
       </c>
       <c r="B221" t="n">
-        <v>6.41</v>
+        <v>23076</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>45944.003</v>
       </c>
       <c r="B222" t="n">
-        <v>6.41</v>
+        <v>23077.2</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45944.00303240741</v>
       </c>
       <c r="B223" t="n">
-        <v>6.41</v>
+        <v>23080</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45944.00310185185</v>
       </c>
       <c r="B224" t="n">
-        <v>6.41</v>
+        <v>23086</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45944.00310185185</v>
       </c>
       <c r="B225" t="n">
-        <v>6.41</v>
+        <v>23086</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>45944.00314814815</v>
       </c>
       <c r="B226" t="n">
-        <v>6.41</v>
+        <v>23090</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45944.00530285879</v>
       </c>
       <c r="B227" t="n">
-        <v>6.47</v>
+        <v>23276.17</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45944.00548611111</v>
       </c>
       <c r="B228" t="n">
-        <v>6.47</v>
+        <v>23292</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45944.00555362269</v>
       </c>
       <c r="B229" t="n">
-        <v>6.47</v>
+        <v>23297.83</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45944.00767361111</v>
       </c>
       <c r="B230" t="n">
-        <v>6.52</v>
+        <v>23481</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45944.00772762732</v>
       </c>
       <c r="B231" t="n">
-        <v>6.52</v>
+        <v>23485.67</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>45944.00773148148</v>
       </c>
       <c r="B232" t="n">
-        <v>6.52</v>
+        <v>23486</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45944.00774305555</v>
       </c>
       <c r="B233" t="n">
-        <v>6.52</v>
+        <v>23487</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45944.00778935185</v>
       </c>
       <c r="B234" t="n">
-        <v>6.53</v>
+        <v>23491</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45944.00780864583</v>
       </c>
       <c r="B235" t="n">
-        <v>6.53</v>
+        <v>23492.67</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>45944.0078125</v>
       </c>
       <c r="B236" t="n">
-        <v>6.53</v>
+        <v>23493</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45944.00810185185</v>
       </c>
       <c r="B237" t="n">
-        <v>6.53</v>
+        <v>23518</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45944.00811342592</v>
       </c>
       <c r="B238" t="n">
-        <v>6.53</v>
+        <v>23519</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>45944.00824074074</v>
       </c>
       <c r="B239" t="n">
-        <v>6.54</v>
+        <v>23530</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>45944.009</v>
       </c>
       <c r="B240" t="n">
-        <v>6.55</v>
+        <v>23595.6</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>45944.015</v>
       </c>
       <c r="B241" t="n">
-        <v>6.7</v>
+        <v>24114</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45944.022</v>
       </c>
       <c r="B242" t="n">
-        <v>6.87</v>
+        <v>24718.8</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45944.07417824074</v>
       </c>
       <c r="B243" t="n">
-        <v>8.119999999999999</v>
+        <v>29227</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45944.07517361111</v>
       </c>
       <c r="B244" t="n">
-        <v>8.140000000000001</v>
+        <v>29313</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45944.07613425926</v>
       </c>
       <c r="B245" t="n">
-        <v>8.17</v>
+        <v>29396</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45944.07710648148</v>
       </c>
       <c r="B246" t="n">
-        <v>8.19</v>
+        <v>29480</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45944.07877314815</v>
       </c>
       <c r="B247" t="n">
-        <v>8.23</v>
+        <v>29624</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45944.08006944445</v>
       </c>
       <c r="B248" t="n">
-        <v>8.26</v>
+        <v>29736</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>45944.09583333333</v>
       </c>
       <c r="B249" t="n">
-        <v>8.640000000000001</v>
+        <v>31098</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45944.11180555556</v>
       </c>
       <c r="B250" t="n">
-        <v>9.02</v>
+        <v>32478</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45944.514</v>
       </c>
       <c r="B251" t="n">
-        <v>18.67</v>
+        <v>67227.60000000001</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45944.7325</v>
       </c>
       <c r="B252" t="n">
-        <v>23.92</v>
+        <v>86106</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45944.89798611111</v>
       </c>
       <c r="B253" t="n">
-        <v>27.89</v>
+        <v>100404</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>45944.93215277778</v>
       </c>
       <c r="B254" t="n">
-        <v>28.71</v>
+        <v>103356</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45945.12222222222</v>
       </c>
       <c r="B255" t="n">
-        <v>33.27</v>
+        <v>119778</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45945.12222222222</v>
       </c>
       <c r="B256" t="n">
-        <v>33.27</v>
+        <v>119778</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>45945.12222222222</v>
       </c>
       <c r="B257" t="n">
-        <v>33.27</v>
+        <v>119778</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45945.23857638889</v>
       </c>
       <c r="B258" t="n">
-        <v>36.06</v>
+        <v>129831</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45945.73431712963</v>
       </c>
       <c r="B259" t="n">
-        <v>47.96</v>
+        <v>172663</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45945.90590277778</v>
       </c>
       <c r="B260" t="n">
-        <v>52.08</v>
+        <v>187488</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>45945.90590277778</v>
       </c>
       <c r="B261" t="n">
-        <v>52.08</v>
+        <v>187488</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45945.90590277778</v>
       </c>
       <c r="B262" t="n">
-        <v>52.08</v>
+        <v>187488</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45946.5578125</v>
       </c>
       <c r="B263" t="n">
-        <v>67.73</v>
+        <v>243813</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45947.70814814815</v>
       </c>
       <c r="B264" t="n">
-        <v>95.33</v>
+        <v>343202</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45947.79552083334</v>
       </c>
       <c r="B265" t="n">
-        <v>97.43000000000001</v>
+        <v>350751</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45948.61255787037</v>
       </c>
       <c r="B266" t="n">
-        <v>117.04</v>
+        <v>421343</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45948.78799768518</v>
       </c>
       <c r="B267" t="n">
-        <v>121.25</v>
+        <v>436501</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>45949.52506944445</v>
       </c>
       <c r="B268" t="n">
-        <v>138.94</v>
+        <v>500184</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45950.78024305555</v>
       </c>
       <c r="B269" t="n">
-        <v>169.06</v>
+        <v>608631</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45950.8330787037</v>
       </c>
       <c r="B270" t="n">
-        <v>170.33</v>
+        <v>613196</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45950.8330787037</v>
       </c>
       <c r="B271" t="n">
-        <v>170.33</v>
+        <v>613196</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>45951.52146990741</v>
       </c>
       <c r="B272" t="n">
-        <v>186.85</v>
+        <v>672673</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45951.71008101852</v>
       </c>
       <c r="B273" t="n">
-        <v>191.38</v>
+        <v>688969</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45952.52082175926</v>
       </c>
       <c r="B274" t="n">
-        <v>210.84</v>
+        <v>759017</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45953.5036574074</v>
       </c>
       <c r="B275" t="n">
-        <v>234.43</v>
+        <v>843934</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45953.80598379629</v>
       </c>
       <c r="B276" t="n">
-        <v>241.68</v>
+        <v>870055</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45954.78755787037</v>
       </c>
       <c r="B277" t="n">
-        <v>265.24</v>
+        <v>954863</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45955.67466435185</v>
       </c>
       <c r="B278" t="n">
-        <v>286.53</v>
+        <v>1031509</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45956.56517361111</v>
       </c>
       <c r="B279" t="n">
-        <v>307.9</v>
+        <v>1108449</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45957.51582175926</v>
       </c>
       <c r="B280" t="n">
-        <v>330.72</v>
+        <v>1190585</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>45958.52263888889</v>
       </c>
       <c r="B281" t="n">
-        <v>354.88</v>
+        <v>1277574</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45958.81748842593</v>
       </c>
       <c r="B282" t="n">
-        <v>361.96</v>
+        <v>1303049</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
